--- a/.agents/skills/proto/assets/Adventure_template/split_xlsx/trophy.xlsx
+++ b/.agents/skills/proto/assets/Adventure_template/split_xlsx/trophy.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,8 @@
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,6 +571,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
@@ -607,6 +619,16 @@
           <t>id</t>
         </is>
       </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -632,12 +654,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>TrophyPet17_Sport_9</t>
+          <t>Pet17_Sport_9</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>TrophyPet17_Sport_9</t>
+          <t>Pet17_Sport_9</t>
         </is>
       </c>
       <c r="H5" s="4" t="n"/>
